--- a/output/xlsx/UC18Vaccinations--GT-.xlsx
+++ b/output/xlsx/UC18Vaccinations--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>4.0</t>
   </si>
   <si>
     <t>Suite Type:</t>

--- a/output/xlsx/UC18Vaccinations--GT-.xlsx
+++ b/output/xlsx/UC18Vaccinations--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>6.0</t>
   </si>
   <si>
     <t>Suite Type:</t>

--- a/output/xlsx/UC18Vaccinations--GT-.xlsx
+++ b/output/xlsx/UC18Vaccinations--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>6.0</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>Suite Type:</t>
